--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_95_R10.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_95_R10.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0977</v>
+        <v>4.0454</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7994</v>
+        <v>4.9488</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7017</v>
+        <v>-0.9033</v>
       </c>
       <c r="G2" t="n">
         <v>3.653</v>
@@ -610,13 +610,13 @@
         <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0914</v>
+        <v>-0.1436</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0351</v>
+        <v>0.1142</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0562</v>
+        <v>-0.2579</v>
       </c>
       <c r="V2" t="n">
         <v>0.5361</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.813</v>
+        <v>3.9452</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3851</v>
+        <v>5.4165</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.5722</v>
+        <v>-1.4714</v>
       </c>
       <c r="G3" t="n">
         <v>4.1429</v>
@@ -688,13 +688,13 @@
         <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5619</v>
+        <v>-0.4296</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0395</v>
+        <v>0.0709</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6014</v>
+        <v>-0.5006</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. DIOUF</t>
+          <t>M. MORGAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.985</v>
+        <v>2.1363</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5236</v>
+        <v>1.9213</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5386</v>
+        <v>0.215</v>
       </c>
       <c r="G4" t="n">
+        <v>3.3118</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.7059</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.606</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.5371</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.6133</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.9238</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-0.2252</v>
+      </c>
+      <c r="N4" t="n">
         <v>0.0926</v>
       </c>
-      <c r="H4" t="n">
-        <v>1.2268</v>
-      </c>
-      <c r="I4" t="n">
-        <v>-1.1342</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.873</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1.9529</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.9201</v>
-      </c>
-      <c r="M4" t="n">
-        <v>-2.7804</v>
-      </c>
-      <c r="N4" t="n">
-        <v>-0.7261</v>
-      </c>
       <c r="O4" t="n">
-        <v>-2.0543</v>
+        <v>-0.3178</v>
       </c>
       <c r="P4" t="n">
-        <v>0.232</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.3917</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5187</v>
+        <v>-0.2478</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9006</v>
+        <v>-0.224</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6181</v>
+        <v>-0.0237</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. MORGAN</t>
+          <t>D. ALSTON JR.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8674</v>
+        <v>2.0202</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9213</v>
+        <v>1.5463</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0539</v>
+        <v>0.4739</v>
       </c>
       <c r="G5" t="n">
-        <v>3.3118</v>
+        <v>2.3161</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7059</v>
+        <v>0.3386</v>
       </c>
       <c r="I5" t="n">
-        <v>1.606</v>
+        <v>1.9774</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5371</v>
+        <v>2.1517</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6133</v>
+        <v>0.0672</v>
       </c>
       <c r="L5" t="n">
-        <v>1.9238</v>
+        <v>2.0844</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2252</v>
+        <v>0.1644</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0926</v>
+        <v>0.2714</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3178</v>
+        <v>-0.107</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5165999999999999</v>
+        <v>-0.2959</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.224</v>
+        <v>-0.3734</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2926</v>
+        <v>0.0775</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. ALSTON JR.</t>
+          <t>K. JALLOW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7849</v>
+        <v>1.6068</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5463</v>
+        <v>2.5421</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2386</v>
+        <v>-0.9353</v>
       </c>
       <c r="G6" t="n">
-        <v>2.3161</v>
+        <v>1.9733</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3386</v>
+        <v>0.2232</v>
       </c>
       <c r="I6" t="n">
-        <v>1.9774</v>
+        <v>1.7501</v>
       </c>
       <c r="J6" t="n">
-        <v>2.1517</v>
+        <v>3.7997</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0672</v>
+        <v>1.1497</v>
       </c>
       <c r="L6" t="n">
-        <v>2.0844</v>
+        <v>2.65</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1644</v>
+        <v>-1.8264</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2714</v>
+        <v>-0.9265</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.107</v>
+        <v>-0.8999</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="R6" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5311</v>
+        <v>-0.5083</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3734</v>
+        <v>-0.0077</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1577</v>
+        <v>-0.5006</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. DIARRA</t>
+          <t>M. DIOUF</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9351</v>
+        <v>0.8643</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0657</v>
+        <v>1.7726</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1307</v>
+        <v>-0.9083</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0384</v>
+        <v>0.0926</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3662</v>
+        <v>1.2268</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3279</v>
+        <v>-1.1342</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7354000000000001</v>
+        <v>2.873</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5881999999999999</v>
+        <v>1.9529</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1472</v>
+        <v>0.9201</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.697</v>
+        <v>-2.7804</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.222</v>
+        <v>-0.7261</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4751</v>
+        <v>-2.0543</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.232</v>
+        <v>0.232</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.6237</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2705</v>
+        <v>0.398</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5623</v>
+        <v>0.1496</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7082000000000001</v>
+        <v>0.2484</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1418</v>
+        <v>0.1418</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. JALLOW</t>
+          <t>C. EDWARDS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7669</v>
+        <v>0.4888</v>
       </c>
       <c r="E8" t="n">
-        <v>1.8029</v>
+        <v>2.0963</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0361</v>
+        <v>-1.6075</v>
       </c>
       <c r="G8" t="n">
-        <v>1.9733</v>
+        <v>4.3191</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2232</v>
+        <v>1.1272</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7501</v>
+        <v>3.1919</v>
       </c>
       <c r="J8" t="n">
-        <v>3.7997</v>
+        <v>7.0496</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1497</v>
+        <v>2.2217</v>
       </c>
       <c r="L8" t="n">
-        <v>2.65</v>
+        <v>4.8279</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.8264</v>
+        <v>-2.7305</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9265</v>
+        <v>-1.0945</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8999</v>
+        <v>-1.636</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-3.2473</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.3917</v>
+        <v>-4.871</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3482</v>
+        <v>-0.5829</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7468</v>
+        <v>-0.0824</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6014</v>
+        <v>-0.5006</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. EDWARDS</t>
+          <t>A. DIARRA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3511</v>
+        <v>-0.0072</v>
       </c>
       <c r="E9" t="n">
-        <v>1.3571</v>
+        <v>0.5939</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7083</v>
+        <v>-0.6011</v>
       </c>
       <c r="G9" t="n">
-        <v>4.3191</v>
+        <v>0.0384</v>
       </c>
       <c r="H9" t="n">
-        <v>1.1272</v>
+        <v>0.3662</v>
       </c>
       <c r="I9" t="n">
-        <v>3.1919</v>
+        <v>-0.3279</v>
       </c>
       <c r="J9" t="n">
-        <v>7.0496</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>2.2217</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>4.8279</v>
+        <v>0.1472</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.7305</v>
+        <v>-0.697</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0945</v>
+        <v>-0.222</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.636</v>
+        <v>-0.4751</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.2473</v>
+        <v>-0.232</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.871</v>
+        <v>-0.232</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6237</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4229</v>
+        <v>0.3282</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8215</v>
+        <v>0.0905</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6014</v>
+        <v>0.2377</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. NIANG</t>
+          <t>D. HACKETT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.828</v>
+        <v>-1.4781</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2182</v>
+        <v>-1.5624</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6098</v>
+        <v>0.0843</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1553</v>
+        <v>-0.2691</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7382</v>
+        <v>0.4502</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8935</v>
+        <v>-0.7194</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6988</v>
+        <v>-0.0331</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1478</v>
+        <v>0.8401999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8465</v>
+        <v>-0.8734</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5434</v>
+        <v>-0.236</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5904</v>
+        <v>-0.39</v>
       </c>
       <c r="O10" t="n">
-        <v>0.047</v>
+        <v>0.154</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6959</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.3917</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1457</v>
+        <v>-0.7451</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5975</v>
+        <v>-0.1375</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5482</v>
+        <v>-0.6075</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. HACKETT</t>
+          <t>S. NIANG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9156</v>
+        <v>-1.4844</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7983</v>
+        <v>-0.1435</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1174</v>
+        <v>-1.3409</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2691</v>
+        <v>0.1553</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4502</v>
+        <v>-0.7382</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7194</v>
+        <v>0.8935</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0331</v>
+        <v>0.6988</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8401999999999999</v>
+        <v>-0.1478</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.8734</v>
+        <v>0.8465</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.236</v>
+        <v>-0.5434</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.39</v>
+        <v>-0.5904</v>
       </c>
       <c r="O11" t="n">
-        <v>0.154</v>
+        <v>0.047</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4639</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.3917</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1826</v>
+        <v>-0.8022</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3734</v>
+        <v>-0.5228</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8092</v>
+        <v>-0.2794</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2428</v>
+        <v>-3.478</v>
       </c>
       <c r="E12" t="n">
         <v>-1.3564</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8863</v>
+        <v>-2.1216</v>
       </c>
       <c r="G12" t="n">
         <v>-0.3634</v>
@@ -1390,13 +1390,13 @@
         <v>0.6959</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0391</v>
+        <v>-0.2743</v>
       </c>
       <c r="T12" t="n">
         <v>-0.3734</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3343</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-2.1444</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.912500000000002</v>
+        <v>8.6593</v>
       </c>
       <c r="E13" t="n">
-        <v>17.0285</v>
+        <v>17.7755</v>
       </c>
       <c r="F13" t="n">
-        <v>-9.116400000000001</v>
+        <v>-9.116199999999999</v>
       </c>
       <c r="G13" t="n">
         <v>19.37</v>
@@ -1468,13 +1468,13 @@
         <v>10.438</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.050300000000001</v>
+        <v>-3.3035</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.0427</v>
+        <v>-1.296</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.0075</v>
+        <v>-2.0076</v>
       </c>
       <c r="V13" t="n">
         <v>-1.6083</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7747</v>
+        <v>5.0715</v>
       </c>
       <c r="E14" t="n">
-        <v>6.6448</v>
+        <v>7.7064</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.8701</v>
+        <v>-2.6348</v>
       </c>
       <c r="G14" t="n">
         <v>2.2282</v>
@@ -1546,13 +1546,13 @@
         <v>2.7834</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0618</v>
+        <v>0.235</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.955</v>
+        <v>0.1065</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1067</v>
+        <v>0.1285</v>
       </c>
       <c r="V14" t="n">
         <v>2.1444</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9618</v>
+        <v>2.1197</v>
       </c>
       <c r="E15" t="n">
-        <v>4.4913</v>
+        <v>3.7836</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.5295</v>
+        <v>-1.6639</v>
       </c>
       <c r="G15" t="n">
         <v>-0.3022</v>
@@ -1624,13 +1624,13 @@
         <v>2.5515</v>
       </c>
       <c r="S15" t="n">
-        <v>1.8723</v>
+        <v>1.0302</v>
       </c>
       <c r="T15" t="n">
-        <v>1.4787</v>
+        <v>0.771</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3936</v>
+        <v>0.2592</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. SWIDER</t>
+          <t>N. WEILER-BABB</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0721</v>
+        <v>0.0393</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1474</v>
+        <v>3.8289</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2195</v>
+        <v>-3.7896</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3862</v>
+        <v>-2.9893</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3193</v>
+        <v>-0.2556</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.067</v>
+        <v>-2.7337</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3714</v>
+        <v>3.2935</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0168</v>
+        <v>1.8149</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3546</v>
+        <v>1.4786</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7577</v>
+        <v>-6.2828</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3361</v>
+        <v>-2.0705</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4216</v>
+        <v>-4.2123</v>
       </c>
       <c r="P16" t="n">
-        <v>0.232</v>
+        <v>2.3195</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.232</v>
+        <v>2.3195</v>
       </c>
       <c r="S16" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.5673</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.224</v>
+        <v>0.3936</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3062</v>
+        <v>0.1737</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. WEILER-BABB</t>
+          <t>C. SWIDER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1287</v>
+        <v>-0.055</v>
       </c>
       <c r="E17" t="n">
-        <v>3.8289</v>
+        <v>0.2653</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.9576</v>
+        <v>-0.3203</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.9893</v>
+        <v>-0.3862</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2556</v>
+        <v>-0.3193</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.7337</v>
+        <v>-0.067</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2935</v>
+        <v>0.3714</v>
       </c>
       <c r="K17" t="n">
-        <v>1.8149</v>
+        <v>0.0168</v>
       </c>
       <c r="L17" t="n">
-        <v>1.4786</v>
+        <v>0.3546</v>
       </c>
       <c r="M17" t="n">
-        <v>-6.2828</v>
+        <v>-0.7577</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.0705</v>
+        <v>-0.3361</v>
       </c>
       <c r="O17" t="n">
-        <v>-4.2123</v>
+        <v>-0.4216</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3195</v>
+        <v>0.232</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3195</v>
+        <v>0.232</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3993</v>
+        <v>0.0993</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3936</v>
+        <v>-0.1061</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0057</v>
+        <v>0.2054</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. LOYD</t>
+          <t>S. HAZER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7606000000000001</v>
+        <v>-0.6919</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3878</v>
+        <v>-0.9422</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1484</v>
+        <v>0.2502</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.4294</v>
+        <v>-0.4504</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.5489</v>
+        <v>-0.4705</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.8804</v>
+        <v>0.0201</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1344</v>
+        <v>0.1072</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2045</v>
+        <v>0.0336</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0701</v>
+        <v>0.0736</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.2949</v>
+        <v>-0.5577</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3444</v>
+        <v>-0.5041</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.9505</v>
+        <v>-0.0535</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6959</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8556</v>
+        <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>1.0425</v>
+        <v>0.0806</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6097</v>
+        <v>-0.0314</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4327</v>
+        <v>0.112</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9304</v>
+        <v>0.1418</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. HAZER</t>
+          <t>J. LOYD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8771</v>
+        <v>-1.0137</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0601</v>
+        <v>0.0339</v>
       </c>
       <c r="F19" t="n">
-        <v>0.183</v>
+        <v>-1.0476</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4504</v>
+        <v>-3.4294</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4705</v>
+        <v>-1.5489</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0201</v>
+        <v>-1.8804</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1072</v>
+        <v>-0.1344</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0336</v>
+        <v>-0.2045</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0736</v>
+        <v>0.0701</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5577</v>
+        <v>-3.2949</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5041</v>
+        <v>-1.3444</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0535</v>
+        <v>-1.9505</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6959</v>
+        <v>1.8556</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1046</v>
+        <v>0.7894</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1494</v>
+        <v>0.2559</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0448</v>
+        <v>0.5335</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1418</v>
+        <v>0.9304</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1578</v>
+        <v>-1.1242</v>
       </c>
       <c r="E20" t="n">
         <v>-0.8653</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2925</v>
+        <v>-0.2589</v>
       </c>
       <c r="G20" t="n">
         <v>-1.2628</v>
@@ -2014,13 +2014,13 @@
         <v>0.232</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.127</v>
+        <v>-0.0934</v>
       </c>
       <c r="T20" t="n">
         <v>-0.1494</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0224</v>
+        <v>0.056</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6247</v>
+        <v>-2.0952</v>
       </c>
       <c r="E21" t="n">
         <v>1.504</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.1287</v>
+        <v>-3.5992</v>
       </c>
       <c r="G21" t="n">
         <v>-1.9936</v>
@@ -2092,13 +2092,13 @@
         <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>0.673</v>
+        <v>0.2025</v>
       </c>
       <c r="T21" t="n">
         <v>0.1221</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5508999999999999</v>
+        <v>0.0804</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5361</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.0064</v>
+        <v>-7.1414</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.1717</v>
+        <v>-5.4076</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8347</v>
+        <v>-1.7339</v>
       </c>
       <c r="G23" t="n">
         <v>-7.9738</v>
@@ -2248,13 +2248,13 @@
         <v>2.7834</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6453</v>
+        <v>0.5102</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4683</v>
+        <v>0.2324</v>
       </c>
       <c r="U23" t="n">
-        <v>0.177</v>
+        <v>0.2779</v>
       </c>
       <c r="V23" t="n">
         <v>-0.1418</v>
@@ -2284,7 +2284,7 @@
         <v>-7.9124</v>
       </c>
       <c r="E24" t="n">
-        <v>9.116299999999999</v>
+        <v>9.116199999999997</v>
       </c>
       <c r="F24" t="n">
         <v>-17.0287</v>
